--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ49"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2502,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130009797</v>
+        <v>136611179</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>92065</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,31 +2513,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2545,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684961</v>
+        <v>684981</v>
       </c>
       <c r="R18" t="n">
-        <v>6562439</v>
+        <v>6562421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,17 +2570,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bearbetad granlåga, fullt av hackspån.</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,6 +2584,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2611,13 +2602,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009797</t>
+          <t>https://artportalen.se/Sighting/136611179</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130114980</v>
+        <v>130009797</v>
       </c>
       <c r="B19" t="n">
         <v>57950</v>
@@ -2645,11 +2636,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
@@ -2660,17 +2647,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684878</v>
+        <v>684961</v>
       </c>
       <c r="R19" t="n">
-        <v>6562610</v>
+        <v>6562439</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2694,22 +2681,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bearbetad granlåga, fullt av hackspån.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,24 +2706,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114980</t>
+          <t>https://artportalen.se/Sighting/130009797</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130114997</v>
+        <v>130114980</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2784,14 +2766,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684941</v>
+        <v>684878</v>
       </c>
       <c r="R20" t="n">
-        <v>6562537</v>
+        <v>6562610</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2823,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,13 +2841,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114997</t>
+          <t>https://artportalen.se/Sighting/130114980</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130121529</v>
+        <v>130114997</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2893,25 +2875,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685144</v>
+        <v>684941</v>
       </c>
       <c r="R21" t="n">
-        <v>6562346</v>
+        <v>6562537</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2940,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,12 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av död stående tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,24 +2954,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121529</t>
+          <t>https://artportalen.se/Sighting/130114997</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130121540</v>
+        <v>130121529</v>
       </c>
       <c r="B22" t="n">
         <v>57950</v>
@@ -3027,10 +3011,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684954</v>
+        <v>685144</v>
       </c>
       <c r="R22" t="n">
-        <v>6562574</v>
+        <v>6562346</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,7 +3046,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3056,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3103,16 +3087,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121540</t>
+          <t>https://artportalen.se/Sighting/130121529</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130121542</v>
+        <v>130121540</v>
       </c>
       <c r="B23" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,27 +3104,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3149,10 +3133,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684957</v>
+        <v>684954</v>
       </c>
       <c r="R23" t="n">
-        <v>6562562</v>
+        <v>6562574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3178,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av död stående tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,21 +3194,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3235,13 +3209,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121542</t>
+          <t>https://artportalen.se/Sighting/130121540</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130121544</v>
+        <v>130121542</v>
       </c>
       <c r="B24" t="n">
         <v>4775</v>
@@ -3281,10 +3255,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684893</v>
+        <v>684957</v>
       </c>
       <c r="R24" t="n">
-        <v>6562601</v>
+        <v>6562562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3316,7 +3290,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3326,7 +3300,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3367,16 +3341,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121544</t>
+          <t>https://artportalen.se/Sighting/130121542</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130121543</v>
+        <v>130121544</v>
       </c>
       <c r="B25" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,21 +3358,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3413,10 +3387,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684897</v>
+        <v>684893</v>
       </c>
       <c r="R25" t="n">
-        <v>6562616</v>
+        <v>6562601</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3448,7 +3422,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3458,7 +3432,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3499,16 +3473,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121543</t>
+          <t>https://artportalen.se/Sighting/130121544</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130115019</v>
+        <v>130121543</v>
       </c>
       <c r="B26" t="n">
-        <v>58327</v>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3516,49 +3490,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684878</v>
+        <v>684897</v>
       </c>
       <c r="R26" t="n">
-        <v>6562610</v>
+        <v>6562616</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3587,7 +3554,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3597,7 +3564,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3608,77 +3575,96 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130115019</t>
+          <t>https://artportalen.se/Sighting/130121543</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129996772</v>
+        <v>130115019</v>
       </c>
       <c r="B27" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684910</v>
+        <v>684878</v>
       </c>
       <c r="R27" t="n">
-        <v>6562543</v>
+        <v>6562610</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3702,12 +3688,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3722,24 +3718,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129996772</t>
+          <t>https://artportalen.se/Sighting/130115019</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130115016</v>
+        <v>129996772</v>
       </c>
       <c r="B28" t="n">
         <v>58114</v>
@@ -3767,32 +3763,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684878</v>
+        <v>684910</v>
       </c>
       <c r="R28" t="n">
-        <v>6562610</v>
+        <v>6562543</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3816,22 +3808,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3846,24 +3828,24 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130115016</t>
+          <t>https://artportalen.se/Sighting/129996772</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130328801</v>
+        <v>130115016</v>
       </c>
       <c r="B29" t="n">
         <v>58114</v>
@@ -3891,28 +3873,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684955</v>
+        <v>684878</v>
       </c>
       <c r="R29" t="n">
-        <v>6562389</v>
+        <v>6562610</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3936,12 +3922,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3956,27 +3952,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328801</t>
+          <t>https://artportalen.se/Sighting/130115016</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134179933</v>
+        <v>130328801</v>
       </c>
       <c r="B30" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4006,7 +4002,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4016,13 +4012,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>684976</v>
+        <v>684955</v>
       </c>
       <c r="R30" t="n">
-        <v>6562378</v>
+        <v>6562389</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4046,12 +4042,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4077,13 +4073,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134179933</t>
+          <t>https://artportalen.se/Sighting/130328801</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134180019</v>
+        <v>134179933</v>
       </c>
       <c r="B31" t="n">
         <v>58136</v>
@@ -4126,10 +4122,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685035</v>
+        <v>684976</v>
       </c>
       <c r="R31" t="n">
-        <v>6562398</v>
+        <v>6562378</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4187,63 +4183,62 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134180019</t>
+          <t>https://artportalen.se/Sighting/134179933</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130114978</v>
+        <v>134180019</v>
       </c>
       <c r="B32" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685149</v>
+        <v>685035</v>
       </c>
       <c r="R32" t="n">
-        <v>6562238</v>
+        <v>6562398</v>
       </c>
       <c r="S32" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4267,22 +4262,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,24 +4282,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth, Irena Koelemeijer</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114978</t>
+          <t>https://artportalen.se/Sighting/134180019</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130121530</v>
+        <v>130114978</v>
       </c>
       <c r="B33" t="n">
         <v>8455</v>
@@ -4342,25 +4327,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685150</v>
+        <v>685149</v>
       </c>
       <c r="R33" t="n">
-        <v>6562245</v>
+        <v>6562238</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4389,7 +4378,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4399,7 +4388,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4410,48 +4399,28 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth, Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121530</t>
+          <t>https://artportalen.se/Sighting/130114978</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130121533</v>
+        <v>130121530</v>
       </c>
       <c r="B34" t="n">
         <v>8455</v>
@@ -4491,10 +4460,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>684997</v>
+        <v>685150</v>
       </c>
       <c r="R34" t="n">
-        <v>6562386</v>
+        <v>6562245</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4526,7 +4495,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4536,7 +4505,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4560,12 +4529,12 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+          <t>Pinus sylvestris # Tallåga</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4582,13 +4551,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121533</t>
+          <t>https://artportalen.se/Sighting/130121530</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130330908</v>
+        <v>130121533</v>
       </c>
       <c r="B35" t="n">
         <v>8455</v>
@@ -4617,25 +4586,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skogen söder om Tyresta by, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>684899</v>
+        <v>684997</v>
       </c>
       <c r="R35" t="n">
-        <v>6562614</v>
+        <v>6562386</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4662,12 +4627,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4676,34 +4651,53 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130330908</t>
+          <t>https://artportalen.se/Sighting/130121533</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116794459</v>
+        <v>130330908</v>
       </c>
       <c r="B36" t="n">
-        <v>56884</v>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4711,43 +4705,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208255</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Skogen söder om Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>684898</v>
+        <v>684899</v>
       </c>
       <c r="R36" t="n">
-        <v>6562545</v>
+        <v>6562614</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4774,12 +4768,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4795,27 +4789,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116794459</t>
+          <t>https://artportalen.se/Sighting/130330908</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127378764</v>
+        <v>116794459</v>
       </c>
       <c r="B37" t="n">
-        <v>56876</v>
+        <v>56884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4823,21 +4817,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208257</v>
+        <v>208255</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4856,10 +4850,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>684991</v>
+        <v>684898</v>
       </c>
       <c r="R37" t="n">
-        <v>6562475</v>
+        <v>6562545</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4886,12 +4880,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4918,16 +4912,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127378764</t>
+          <t>https://artportalen.se/Sighting/116794459</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133964707</v>
+        <v>127378764</v>
       </c>
       <c r="B38" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4960,11 +4954,7 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4972,10 +4962,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>684926</v>
+        <v>684991</v>
       </c>
       <c r="R38" t="n">
-        <v>6562530</v>
+        <v>6562475</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5002,17 +4992,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På ridvägen med krossat huvud.</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5039,13 +5024,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133964707</t>
+          <t>https://artportalen.se/Sighting/127378764</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134003472</v>
+        <v>133964707</v>
       </c>
       <c r="B39" t="n">
         <v>56896</v>
@@ -5081,7 +5066,11 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5089,10 +5078,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>684886</v>
+        <v>684926</v>
       </c>
       <c r="R39" t="n">
-        <v>6562537</v>
+        <v>6562530</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5119,17 +5108,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På ridvägen.</t>
+          <t>På ridvägen med krossat huvud.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5156,16 +5145,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134003472</t>
+          <t>https://artportalen.se/Sighting/133964707</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133965707</v>
+        <v>134003472</v>
       </c>
       <c r="B40" t="n">
-        <v>98219</v>
+        <v>56896</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,38 +5162,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219815</v>
+        <v>208257</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685126</v>
+        <v>684886</v>
       </c>
       <c r="R40" t="n">
-        <v>6562254</v>
+        <v>6562537</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5231,12 +5225,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På ridvägen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5263,16 +5262,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965707</t>
+          <t>https://artportalen.se/Sighting/134003472</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115521263</v>
+        <v>133965707</v>
       </c>
       <c r="B41" t="n">
-        <v>106244</v>
+        <v>98219</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5280,21 +5279,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>219815</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5304,14 +5303,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>684827</v>
+        <v>685126</v>
       </c>
       <c r="R41" t="n">
-        <v>6562598</v>
+        <v>6562254</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5338,12 +5337,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5370,16 +5369,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115521263</t>
+          <t>https://artportalen.se/Sighting/133965707</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130121584</v>
+        <v>115521263</v>
       </c>
       <c r="B42" t="n">
-        <v>106243</v>
+        <v>106244</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5406,26 +5405,22 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685013</v>
+        <v>684827</v>
       </c>
       <c r="R42" t="n">
-        <v>6562405</v>
+        <v>6562598</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5449,17 +5444,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Flera plantor</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5475,27 +5465,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121584</t>
+          <t>https://artportalen.se/Sighting/115521263</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134440544</v>
+        <v>130121584</v>
       </c>
       <c r="B43" t="n">
-        <v>106324</v>
+        <v>106243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5524,24 +5514,24 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685174</v>
+        <v>685013</v>
       </c>
       <c r="R43" t="n">
-        <v>6562279</v>
+        <v>6562405</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5565,17 +5555,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav två med blomstänglar.</t>
+          <t>Flera plantor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5591,24 +5581,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440544</t>
+          <t>https://artportalen.se/Sighting/130121584</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134440598</v>
+        <v>134440544</v>
       </c>
       <c r="B44" t="n">
         <v>106324</v>
@@ -5640,7 +5630,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -5651,10 +5641,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685131</v>
+        <v>685174</v>
       </c>
       <c r="R44" t="n">
-        <v>6562317</v>
+        <v>6562279</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5691,7 +5681,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav en med blomstängel.</t>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5718,16 +5708,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440598</t>
+          <t>https://artportalen.se/Sighting/134440544</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130121531</v>
+        <v>134440598</v>
       </c>
       <c r="B45" t="n">
-        <v>97983</v>
+        <v>106324</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5735,34 +5725,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685093</v>
+        <v>685131</v>
       </c>
       <c r="R45" t="n">
-        <v>6562301</v>
+        <v>6562317</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5789,22 +5787,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5813,33 +5806,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121531</t>
+          <t>https://artportalen.se/Sighting/134440598</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130110447</v>
+        <v>130121531</v>
       </c>
       <c r="B46" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5847,16 +5841,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5867,14 +5861,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>684940</v>
+        <v>685093</v>
       </c>
       <c r="R46" t="n">
-        <v>6562551</v>
+        <v>6562301</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5904,9 +5898,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5921,24 +5925,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130110447</t>
+          <t>https://artportalen.se/Sighting/130121531</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130115022</v>
+        <v>130110447</v>
       </c>
       <c r="B47" t="n">
         <v>97986</v>
@@ -5967,23 +5971,19 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Tyresta, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>684878</v>
+        <v>684940</v>
       </c>
       <c r="R47" t="n">
-        <v>6562610</v>
+        <v>6562551</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6010,19 +6010,9 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6037,27 +6027,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130115022</t>
+          <t>https://artportalen.se/Sighting/130110447</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133965744</v>
+        <v>130115022</v>
       </c>
       <c r="B48" t="n">
-        <v>98249</v>
+        <v>97986</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6065,21 +6055,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>223358</v>
+        <v>221946</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6089,17 +6079,17 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685126</v>
+        <v>684878</v>
       </c>
       <c r="R48" t="n">
-        <v>6562254</v>
+        <v>6562610</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6123,12 +6113,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6137,69 +6137,72 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965744</t>
+          <t>https://artportalen.se/Sighting/130115022</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130121534</v>
+        <v>133965744</v>
       </c>
       <c r="B49" t="n">
-        <v>92328</v>
+        <v>98249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6040162</v>
+        <v>223358</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>684997</v>
+        <v>685126</v>
       </c>
       <c r="R49" t="n">
-        <v>6562398</v>
+        <v>6562254</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6226,22 +6229,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6250,42 +6243,155 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965744</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130121534</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130121534</t>
         </is>
@@ -6341,6 +6447,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>136611179</v>
       </c>
       <c r="B18" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>136611179</v>
       </c>
       <c r="B18" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>136611179</v>
       </c>
       <c r="B18" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -2505,7 +2505,7 @@
         <v>136611179</v>
       </c>
       <c r="B18" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>136611179</v>
       </c>
       <c r="B9" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>136611179</v>
       </c>
       <c r="B9" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>136611179</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>136611179</v>
       </c>
       <c r="B9" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>136611179</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>136611179</v>
       </c>
       <c r="B9" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>136611179</v>
       </c>
       <c r="B9" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2619,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133965707</v>
+        <v>137308668</v>
       </c>
       <c r="B19" t="n">
-        <v>98219</v>
+        <v>56954</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,38 +2630,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219815</v>
+        <v>208257</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685126</v>
+        <v>685001</v>
       </c>
       <c r="R19" t="n">
-        <v>6562254</v>
+        <v>6562482</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,12 +2693,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,16 +2725,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965707</t>
+          <t>https://artportalen.se/Sighting/137308668</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130121584</v>
+        <v>133965707</v>
       </c>
       <c r="B20" t="n">
-        <v>106243</v>
+        <v>98219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2737,45 +2742,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>219815</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685013</v>
+        <v>685126</v>
       </c>
       <c r="R20" t="n">
-        <v>6562405</v>
+        <v>6562254</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,17 +2800,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera plantor</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,27 +2821,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121584</t>
+          <t>https://artportalen.se/Sighting/133965707</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134440544</v>
+        <v>130121584</v>
       </c>
       <c r="B21" t="n">
-        <v>106324</v>
+        <v>106243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2874,24 +2870,24 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685174</v>
+        <v>685013</v>
       </c>
       <c r="R21" t="n">
-        <v>6562279</v>
+        <v>6562405</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2915,17 +2911,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav två med blomstänglar.</t>
+          <t>Flera plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2941,24 +2937,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440544</t>
+          <t>https://artportalen.se/Sighting/130121584</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134440598</v>
+        <v>134440544</v>
       </c>
       <c r="B22" t="n">
         <v>106324</v>
@@ -2990,7 +2986,7 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3001,10 +2997,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685131</v>
+        <v>685174</v>
       </c>
       <c r="R22" t="n">
-        <v>6562317</v>
+        <v>6562279</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3041,7 +3037,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav en med blomstängel.</t>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3068,16 +3064,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440598</t>
+          <t>https://artportalen.se/Sighting/134440544</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130121531</v>
+        <v>134440598</v>
       </c>
       <c r="B23" t="n">
-        <v>97983</v>
+        <v>106324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3085,34 +3081,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685093</v>
+        <v>685131</v>
       </c>
       <c r="R23" t="n">
-        <v>6562301</v>
+        <v>6562317</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,22 +3143,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,33 +3162,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121531</t>
+          <t>https://artportalen.se/Sighting/134440598</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133965744</v>
+        <v>130121531</v>
       </c>
       <c r="B24" t="n">
-        <v>98249</v>
+        <v>97983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,38 +3197,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223358</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685126</v>
+        <v>685093</v>
       </c>
       <c r="R24" t="n">
-        <v>6562254</v>
+        <v>6562301</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3255,12 +3251,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3269,69 +3275,72 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965744</t>
+          <t>https://artportalen.se/Sighting/130121531</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130121534</v>
+        <v>133965744</v>
       </c>
       <c r="B25" t="n">
-        <v>92328</v>
+        <v>98249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040162</v>
+        <v>223358</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684997</v>
+        <v>685126</v>
       </c>
       <c r="R25" t="n">
-        <v>6562398</v>
+        <v>6562254</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3358,22 +3367,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,42 +3381,155 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965744</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130121534</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130121534</t>
         </is>
@@ -3449,6 +3561,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>137308668</v>
       </c>
       <c r="B19" t="n">
-        <v>56954</v>
+        <v>56955</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130121591</v>
+        <v>137385414</v>
       </c>
       <c r="B6" t="n">
-        <v>97394</v>
+        <v>96997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,17 +1163,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>684947</v>
+        <v>685117</v>
       </c>
       <c r="R6" t="n">
-        <v>6562470</v>
+        <v>6562395</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,12 +1197,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med kuddar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,27 +1223,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121591</t>
+          <t>https://artportalen.se/Sighting/137385414</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130121575</v>
+        <v>130121591</v>
       </c>
       <c r="B7" t="n">
-        <v>91872</v>
+        <v>97394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,37 +1251,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684978</v>
+        <v>684947</v>
       </c>
       <c r="R7" t="n">
-        <v>6562421</v>
+        <v>6562470</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,71 +1323,75 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121575</t>
+          <t>https://artportalen.se/Sighting/130121591</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130121576</v>
+        <v>137385323</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684977</v>
+        <v>685179</v>
       </c>
       <c r="R8" t="n">
-        <v>6562420</v>
+        <v>6562298</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,33 +1429,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121576</t>
+          <t>https://artportalen.se/Sighting/137385323</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136611179</v>
+        <v>130121575</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,22 +1482,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684981</v>
+        <v>684978</v>
       </c>
       <c r="R9" t="n">
         <v>6562421</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,12 +1518,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,34 +1532,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136611179</t>
+          <t>https://artportalen.se/Sighting/130121575</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130009797</v>
+        <v>130121576</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,45 +1566,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684961</v>
+        <v>684977</v>
       </c>
       <c r="R10" t="n">
-        <v>6562439</v>
+        <v>6562420</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,17 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetad granlåga, fullt av hackspån.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,27 +1640,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009797</t>
+          <t>https://artportalen.se/Sighting/130121576</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130121529</v>
+        <v>136611179</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>92106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,39 +1668,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685144</v>
+        <v>684981</v>
       </c>
       <c r="R11" t="n">
-        <v>6562346</v>
+        <v>6562421</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,27 +1725,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av död stående tall.</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,55 +1739,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121529</t>
+          <t>https://artportalen.se/Sighting/136611179</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130328801</v>
+        <v>130009797</v>
       </c>
       <c r="B12" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,7 +1796,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1825,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684955</v>
+        <v>684961</v>
       </c>
       <c r="R12" t="n">
-        <v>6562389</v>
+        <v>6562439</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,12 +1836,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bearbetad granlåga, fullt av hackspån.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,59 +1872,56 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328801</t>
+          <t>https://artportalen.se/Sighting/130009797</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134179933</v>
+        <v>130121529</v>
       </c>
       <c r="B13" t="n">
-        <v>58136</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684976</v>
+        <v>685144</v>
       </c>
       <c r="R13" t="n">
-        <v>6562378</v>
+        <v>6562346</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,12 +1948,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av död stående tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,27 +1983,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134179933</t>
+          <t>https://artportalen.se/Sighting/130121529</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134180019</v>
+        <v>130328801</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2033,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2045,13 +2043,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685035</v>
+        <v>684955</v>
       </c>
       <c r="R14" t="n">
-        <v>6562398</v>
+        <v>6562389</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2075,12 +2073,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,63 +2104,62 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134180019</t>
+          <t>https://artportalen.se/Sighting/130328801</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130114978</v>
+        <v>134179933</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685149</v>
+        <v>684976</v>
       </c>
       <c r="R15" t="n">
-        <v>6562238</v>
+        <v>6562378</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,22 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,67 +2203,70 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth, Irena Koelemeijer</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114978</t>
+          <t>https://artportalen.se/Sighting/134179933</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130121530</v>
+        <v>134180019</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685150</v>
+        <v>685035</v>
       </c>
       <c r="R16" t="n">
-        <v>6562245</v>
+        <v>6562398</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,22 +2293,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,48 +2309,28 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121530</t>
+          <t>https://artportalen.se/Sighting/134180019</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130121533</v>
+        <v>130114978</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2398,25 +2358,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684997</v>
+        <v>685149</v>
       </c>
       <c r="R17" t="n">
-        <v>6562386</v>
+        <v>6562238</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2445,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,51 +2430,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth, Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121533</t>
+          <t>https://artportalen.se/Sighting/130114978</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127378764</v>
+        <v>130121530</v>
       </c>
       <c r="B18" t="n">
-        <v>56876</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2518,43 +2462,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208257</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684991</v>
+        <v>685150</v>
       </c>
       <c r="R18" t="n">
-        <v>6562475</v>
+        <v>6562245</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,12 +2521,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,34 +2545,53 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127378764</t>
+          <t>https://artportalen.se/Sighting/130121530</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137308668</v>
+        <v>130121533</v>
       </c>
       <c r="B19" t="n">
-        <v>56955</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2630,43 +2599,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208257</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685001</v>
+        <v>684997</v>
       </c>
       <c r="R19" t="n">
-        <v>6562482</v>
+        <v>6562386</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,12 +2658,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,34 +2682,53 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308668</t>
+          <t>https://artportalen.se/Sighting/130121533</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133965707</v>
+        <v>127378764</v>
       </c>
       <c r="B20" t="n">
-        <v>98219</v>
+        <v>56876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2742,38 +2736,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219815</v>
+        <v>208257</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685126</v>
+        <v>684991</v>
       </c>
       <c r="R20" t="n">
-        <v>6562254</v>
+        <v>6562475</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2800,12 +2799,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,16 +2831,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965707</t>
+          <t>https://artportalen.se/Sighting/127378764</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130121584</v>
+        <v>137308668</v>
       </c>
       <c r="B21" t="n">
-        <v>106243</v>
+        <v>56955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,45 +2848,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>208257</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685013</v>
+        <v>685001</v>
       </c>
       <c r="R21" t="n">
-        <v>6562405</v>
+        <v>6562482</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,17 +2911,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera plantor</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,27 +2932,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121584</t>
+          <t>https://artportalen.se/Sighting/137308668</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134440544</v>
+        <v>133965707</v>
       </c>
       <c r="B22" t="n">
-        <v>106324</v>
+        <v>98219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,30 +2960,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>219815</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2997,10 +2988,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685174</v>
+        <v>685126</v>
       </c>
       <c r="R22" t="n">
-        <v>6562279</v>
+        <v>6562254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,17 +3018,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ett flertal plantor varav två med blomstänglar.</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,16 +3050,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440544</t>
+          <t>https://artportalen.se/Sighting/133965707</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134440598</v>
+        <v>130121584</v>
       </c>
       <c r="B23" t="n">
-        <v>106324</v>
+        <v>106243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,24 +3088,24 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685131</v>
+        <v>685013</v>
       </c>
       <c r="R23" t="n">
-        <v>6562317</v>
+        <v>6562405</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3143,17 +3129,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav en med blomstängel.</t>
+          <t>Flera plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3169,27 +3155,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440598</t>
+          <t>https://artportalen.se/Sighting/130121584</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130121531</v>
+        <v>134440544</v>
       </c>
       <c r="B24" t="n">
-        <v>97983</v>
+        <v>106324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,34 +3183,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685093</v>
+        <v>685174</v>
       </c>
       <c r="R24" t="n">
-        <v>6562301</v>
+        <v>6562279</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,22 +3245,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,33 +3264,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121531</t>
+          <t>https://artportalen.se/Sighting/134440544</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133965744</v>
+        <v>134440598</v>
       </c>
       <c r="B25" t="n">
-        <v>98249</v>
+        <v>106324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3309,26 +3299,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223358</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3337,10 +3331,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685126</v>
+        <v>685131</v>
       </c>
       <c r="R25" t="n">
-        <v>6562254</v>
+        <v>6562317</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3367,12 +3361,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,38 +3398,38 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965744</t>
+          <t>https://artportalen.se/Sighting/134440598</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130121534</v>
+        <v>130121531</v>
       </c>
       <c r="B26" t="n">
-        <v>92328</v>
+        <v>97983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040162</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3440,10 +3439,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684997</v>
+        <v>685093</v>
       </c>
       <c r="R26" t="n">
-        <v>6562398</v>
+        <v>6562301</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,7 +3474,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3485,7 +3484,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3496,26 +3495,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3525,11 +3504,250 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121531</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133965744</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>685126</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6562254</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965744</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130121534</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130121534</t>
         </is>
@@ -3562,6 +3780,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,45 +795,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130111638</v>
+        <v>137400881</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>96849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lingonliden, Lingonliden, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684950</v>
+        <v>685092</v>
       </c>
       <c r="R3" t="n">
-        <v>6562437</v>
+        <v>6562355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,22 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,30 +882,31 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130111638</t>
+          <t>https://artportalen.se/Sighting/137400881</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130121579</v>
+        <v>130111638</v>
       </c>
       <c r="B4" t="n">
         <v>91909</v>
@@ -936,22 +935,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Lingonliden, Lingonliden, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>684952</v>
+        <v>684950</v>
       </c>
       <c r="R4" t="n">
-        <v>6562436</v>
+        <v>6562437</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,14 +974,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Intressant vit svamp ovanpå som skulle kunna vara begynnande ulltickeporing (såg inga tydliga porer, så antagligen tickdyna eller någon annan generalist art), kollade på ulltickan som definitivt var död på en fallen bit av granen men ingen svamp ovanpå den.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,79 +995,74 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121579</t>
+          <t>https://artportalen.se/Sighting/130111638</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135324359</v>
+        <v>130121579</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2051</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685200</v>
+        <v>684952</v>
       </c>
       <c r="R5" t="n">
-        <v>6562241</v>
+        <v>6562436</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,12 +1086,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Intressant vit svamp ovanpå som skulle kunna vara begynnande ulltickeporing (såg inga tydliga porer, så antagligen tickdyna eller någon annan generalist art), kollade på ulltickan som definitivt var död på en fallen bit av granen men ingen svamp ovanpå den.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,55 +1112,58 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135324359</t>
+          <t>https://artportalen.se/Sighting/130121579</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137385414</v>
+        <v>135324359</v>
       </c>
       <c r="B6" t="n">
-        <v>96997</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685117</v>
+        <v>685200</v>
       </c>
       <c r="R6" t="n">
-        <v>6562395</v>
+        <v>6562241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,17 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med kuddar.</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1233,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137385414</t>
+          <t>https://artportalen.se/Sighting/135324359</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130121591</v>
+        <v>137385414</v>
       </c>
       <c r="B7" t="n">
-        <v>97394</v>
+        <v>97003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,17 +1274,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684947</v>
+        <v>685117</v>
       </c>
       <c r="R7" t="n">
-        <v>6562470</v>
+        <v>6562395</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,12 +1308,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med kuddar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,68 +1334,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121591</t>
+          <t>https://artportalen.se/Sighting/137385414</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137385323</v>
+        <v>130121591</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>97394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685179</v>
+        <v>684947</v>
       </c>
       <c r="R8" t="n">
-        <v>6562298</v>
+        <v>6562470</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,12 +1420,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,65 +1441,68 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137385323</t>
+          <t>https://artportalen.se/Sighting/130121591</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130121575</v>
+        <v>137385323</v>
       </c>
       <c r="B9" t="n">
-        <v>91872</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684978</v>
+        <v>685179</v>
       </c>
       <c r="R9" t="n">
-        <v>6562421</v>
+        <v>6562298</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1518,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1532,30 +1540,31 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121575</t>
+          <t>https://artportalen.se/Sighting/137385323</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130121576</v>
+        <v>130121575</v>
       </c>
       <c r="B10" t="n">
         <v>91872</v>
@@ -1590,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684977</v>
+        <v>684978</v>
       </c>
       <c r="R10" t="n">
-        <v>6562420</v>
+        <v>6562421</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1651,16 +1660,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121576</t>
+          <t>https://artportalen.se/Sighting/130121575</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136611179</v>
+        <v>130121576</v>
       </c>
       <c r="B11" t="n">
-        <v>92106</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,22 +1695,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684981</v>
+        <v>684977</v>
       </c>
       <c r="R11" t="n">
-        <v>6562421</v>
+        <v>6562420</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,12 +1731,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,34 +1745,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136611179</t>
+          <t>https://artportalen.se/Sighting/130121576</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130009797</v>
+        <v>136611179</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,31 +1779,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684961</v>
+        <v>684981</v>
       </c>
       <c r="R12" t="n">
-        <v>6562439</v>
+        <v>6562421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,17 +1836,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Bearbetad granlåga, fullt av hackspån.</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,6 +1850,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1872,56 +1868,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009797</t>
+          <t>https://artportalen.se/Sighting/136611179</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130121529</v>
+        <v>137401065</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>93507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685144</v>
+        <v>685169</v>
       </c>
       <c r="R13" t="n">
-        <v>6562346</v>
+        <v>6562363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,27 +1942,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av död stående tall.</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,55 +1956,56 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121529</t>
+          <t>https://artportalen.se/Sighting/137401065</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130328801</v>
+        <v>130009797</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2033,7 +2013,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2043,13 +2023,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684955</v>
+        <v>684961</v>
       </c>
       <c r="R14" t="n">
-        <v>6562389</v>
+        <v>6562439</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,12 +2053,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetad granlåga, fullt av hackspån.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,59 +2089,56 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328801</t>
+          <t>https://artportalen.se/Sighting/130009797</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134179933</v>
+        <v>130121529</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>684976</v>
+        <v>685144</v>
       </c>
       <c r="R15" t="n">
-        <v>6562378</v>
+        <v>6562346</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,12 +2165,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av död stående tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,70 +2200,70 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134179933</t>
+          <t>https://artportalen.se/Sighting/130121529</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134180019</v>
+        <v>137401060</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>58032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685035</v>
+        <v>685170</v>
       </c>
       <c r="R16" t="n">
-        <v>6562398</v>
+        <v>6562297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,12 +2290,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bearbetad granraka.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,63 +2326,62 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134180019</t>
+          <t>https://artportalen.se/Sighting/137401060</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130114978</v>
+        <v>130328801</v>
       </c>
       <c r="B17" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685149</v>
+        <v>684955</v>
       </c>
       <c r="R17" t="n">
-        <v>6562238</v>
+        <v>6562389</v>
       </c>
       <c r="S17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2404,22 +2405,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2434,67 +2425,70 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth, Irena Koelemeijer</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114978</t>
+          <t>https://artportalen.se/Sighting/130328801</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130121530</v>
+        <v>134179933</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685150</v>
+        <v>684976</v>
       </c>
       <c r="R18" t="n">
-        <v>6562245</v>
+        <v>6562378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,22 +2515,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,91 +2531,74 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121530</t>
+          <t>https://artportalen.se/Sighting/134179933</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130121533</v>
+        <v>134180019</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684997</v>
+        <v>685035</v>
       </c>
       <c r="R19" t="n">
-        <v>6562386</v>
+        <v>6562398</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,22 +2625,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:48</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,95 +2641,70 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121533</t>
+          <t>https://artportalen.se/Sighting/134180019</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127378764</v>
+        <v>137400925</v>
       </c>
       <c r="B20" t="n">
-        <v>56876</v>
+        <v>58196</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208257</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684991</v>
+        <v>685129</v>
       </c>
       <c r="R20" t="n">
-        <v>6562475</v>
+        <v>6562277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,12 +2731,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,7 +2745,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2831,16 +2762,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127378764</t>
+          <t>https://artportalen.se/Sighting/137400925</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137308668</v>
+        <v>137400937</v>
       </c>
       <c r="B21" t="n">
-        <v>56955</v>
+        <v>58191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,43 +2779,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208257</v>
+        <v>103023</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685001</v>
+        <v>685125</v>
       </c>
       <c r="R21" t="n">
-        <v>6562482</v>
+        <v>6562280</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2911,12 +2837,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,7 +2851,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2943,16 +2868,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137308668</t>
+          <t>https://artportalen.se/Sighting/137400937</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133965707</v>
+        <v>130114978</v>
       </c>
       <c r="B22" t="n">
-        <v>98219</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,41 +2885,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219815</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685126</v>
+        <v>685149</v>
       </c>
       <c r="R22" t="n">
-        <v>6562254</v>
+        <v>6562238</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3018,12 +2948,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,34 +2972,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth, Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965707</t>
+          <t>https://artportalen.se/Sighting/130114978</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130121584</v>
+        <v>130121530</v>
       </c>
       <c r="B23" t="n">
-        <v>106243</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3067,45 +3006,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685013</v>
+        <v>685150</v>
       </c>
       <c r="R23" t="n">
-        <v>6562405</v>
+        <v>6562245</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3132,14 +3068,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera plantor</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,34 +3089,53 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121584</t>
+          <t>https://artportalen.se/Sighting/130121530</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134440544</v>
+        <v>130121533</v>
       </c>
       <c r="B24" t="n">
-        <v>106324</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,42 +3143,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685174</v>
+        <v>684997</v>
       </c>
       <c r="R24" t="n">
-        <v>6562279</v>
+        <v>6562386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3245,17 +3202,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ett flertal plantor varav två med blomstänglar.</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,34 +3226,53 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440544</t>
+          <t>https://artportalen.se/Sighting/130121533</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134440598</v>
+        <v>127378764</v>
       </c>
       <c r="B25" t="n">
-        <v>106324</v>
+        <v>56876</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,42 +3280,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>208257</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685131</v>
+        <v>684991</v>
       </c>
       <c r="R25" t="n">
-        <v>6562317</v>
+        <v>6562475</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,17 +3343,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ett flertal plantor varav en med blomstängel.</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,16 +3375,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440598</t>
+          <t>https://artportalen.se/Sighting/127378764</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130121531</v>
+        <v>137308668</v>
       </c>
       <c r="B26" t="n">
-        <v>97983</v>
+        <v>56955</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3415,34 +3392,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>208257</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685093</v>
+        <v>685001</v>
       </c>
       <c r="R26" t="n">
-        <v>6562301</v>
+        <v>6562482</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3469,22 +3455,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3493,33 +3469,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121531</t>
+          <t>https://artportalen.se/Sighting/137308668</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133965744</v>
+        <v>133965707</v>
       </c>
       <c r="B27" t="n">
-        <v>98249</v>
+        <v>98219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,21 +3504,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223358</v>
+        <v>219815</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3617,54 +3594,62 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965744</t>
+          <t>https://artportalen.se/Sighting/133965707</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130121534</v>
+        <v>130121584</v>
       </c>
       <c r="B28" t="n">
-        <v>92328</v>
+        <v>106243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040162</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684997</v>
+        <v>685013</v>
       </c>
       <c r="R28" t="n">
-        <v>6562398</v>
+        <v>6562405</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3691,19 +3676,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:45</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3712,42 +3692,606 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121584</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134440544</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>685174</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6562279</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134440544</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134440598</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>685131</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6562317</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134440598</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130121531</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>685093</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6562301</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121531</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133965744</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>685126</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6562254</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965744</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130121534</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130121534</t>
         </is>
@@ -3782,6 +4326,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137400881</v>
       </c>
       <c r="B3" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137385414</v>
       </c>
       <c r="B7" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137385323</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137401065</v>
       </c>
       <c r="B13" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137400881</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137385414</v>
       </c>
       <c r="B7" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137385323</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137401065</v>
       </c>
       <c r="B13" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137400881</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137385414</v>
       </c>
       <c r="B7" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137385323</v>
       </c>
       <c r="B9" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137401065</v>
       </c>
       <c r="B13" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>137400881</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137385414</v>
       </c>
       <c r="B7" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137385323</v>
       </c>
       <c r="B9" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137401065</v>
       </c>
       <c r="B13" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>137401060</v>
       </c>
       <c r="B16" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>137400925</v>
       </c>
       <c r="B20" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>137400937</v>
       </c>
       <c r="B21" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>137308668</v>
       </c>
       <c r="B26" t="n">
-        <v>56955</v>
+        <v>56958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
